--- a/test/result_2.xlsx
+++ b/test/result_2.xlsx
@@ -333,17 +333,42 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -364,11 +389,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -389,11 +414,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -414,11 +439,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -439,11 +464,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="13" name="Image 13" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -464,11 +489,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -489,11 +514,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -514,11 +539,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -539,11 +564,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -564,11 +589,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -589,11 +614,36 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -614,11 +664,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="20" name="Image 20" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -639,11 +689,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="21" name="Image 21" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -664,11 +714,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="22" name="Image 22" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -689,11 +739,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="23" name="Image 23" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -714,11 +764,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -739,11 +789,36 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="25" name="Image 25" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -764,11 +839,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -789,11 +864,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="27" name="Image 27" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -814,11 +889,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -839,11 +914,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -864,11 +939,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="30" name="Image 30" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -889,11 +964,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="31" name="Image 31" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -914,11 +989,36 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="32" name="Image 32" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -939,11 +1039,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="33" name="Image 33" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -964,11 +1064,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -989,11 +1089,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="35" name="Image 35" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1014,11 +1114,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="36" name="Image 36" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1039,11 +1139,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="37" name="Image 37" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1064,11 +1164,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="38" name="Image 38" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1089,11 +1189,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="39" name="Image 39" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1114,11 +1214,36 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="40" name="Image 40" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2286000" cy="1428750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1139,11 +1264,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="41" name="Image 41" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1164,11 +1289,11 @@
     <ext cx="2286000" cy="1428750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="42" name="Image 42" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1682,7 +1807,7 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, stock_code, report_year, report_period, operating_expense_cost_of_sales FROM income_sheet WHERE (stock_abbr='昭衍新药' OR stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, operating_expense_cost_of_sales FROM income_sheet WHERE (stock_abbr='昭衍新药') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
@@ -1699,7 +1824,7 @@
     {
       "Q": "昭衍新药2025年第三季度销售毛利率是多少？利润表中（营业收入-营业成本）/营业收入*100",
       "A": "昭衍新药 2025三季报的营业成本为 7.73 亿元",
-      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, operating_expense_cost_of_sales FROM income_sheet WHERE (stock_abbr='昭衍新药' OR stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, operating_expense_cost_of_sales FROM income_sheet WHERE (stock_abbr='昭衍新药') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B3004_1.jpg"
     }
   ]
@@ -1746,7 +1871,7 @@
   "子问题": [
     {
       "Q": "计算2025年第三季度各公司的资产负债率，找出资产负债率最高的公司，列出简称和资产负债率（%）",
-      "A": "资产负债率 排名 Top5：1) 凯莱英 —; 2) 迪安诊断 —; 3) 泰格医药 —; 4) 迈普医学 —; 5) 百普赛斯 —",
+      "A": "资产负债率 排名 Top5：1) 迪安诊断 41.25%; 2) 百诚医药 34.49%; 3) 药明康德 24.45%; 4) 泰格医药 14.16%; 5) 凯莱英 12.35%",
       "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, asset_liability_ratio FROM balance_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') ORDER BY asset_liability_ratio DESC LIMIT 10",
       "image": "B3005_1.jpg"
     }
@@ -1922,7 +2047,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, stock_code, report_year, report_period, net_profit_margin FROM core_performance_indicators_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') AND net_profit_margin &gt; 20.0 AND net_profit_margin IS NOT NULL ORDER BY net_profit_margin DESC LIMIT 50</t>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, net_profit_margin FROM core_performance_indicators_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_profit_margin &gt; 20.0 AND net_profit_margin IS NOT NULL ORDER BY net_profit_margin DESC LIMIT 50</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -1938,15 +2063,19 @@
   "子问题": [
     {
       "Q": "2025年第三季度，销售净利率（净利润/营业总收入*100）超过20%的公司有哪些？请列出简称和销售净利率",
-      "A": "未查询到数据",
-      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_profit_margin FROM core_performance_indicators_sheet WHERE (stock_code='000100') AND report_year IN (2025) AND report_period IN ('Q3') AND net_profit_margin &gt; 20.0 AND net_profit_margin IS NOT NULL ORDER BY net_profit_margin DESC LIMIT 50",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr"/>
+      "A": "符合条件共 2 家，前2：药明康德(603259) 37.15%; 成都先导(688222) 24.81%",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_profit_margin FROM core_performance_indicators_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_profit_margin &gt; 20.0 AND net_profit_margin IS NOT NULL ORDER BY net_profit_margin DESC LIMIT 50",
+      "image": "B3009_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>B3009_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
@@ -2126,7 +2255,7 @@
   "子问题": [
     {
       "Q": "2025年第三季度，10家公司的平均销售毛利率是多少？同时列出销售毛利率低于均值的公司",
-      "A": "毛利率均值：—",
+      "A": "毛利率均值：49.61%",
       "SQL": "SELECT AVG(gross_profit_margin) AS gross_profit_margin_avg FROM core_performance_indicators_sheet WHERE gross_profit_margin IS NOT NULL AND report_year IN (2025) AND report_period IN ('Q3')",
       "image": "B3013_1.jpg"
     }
@@ -2318,7 +2447,7 @@
   "子问题": [
     {
       "Q": "比较凯莱英、药明康德、泰格医药2025年第三季度的销售毛利率，用条形图展示",
-      "A": "毛利率 对比：凯莱英 2025三季报 —; 泰格医药 2025三季报 —; 药明康德 2025三季报 —",
+      "A": "毛利率 对比：凯莱英 2025三季报 —; 泰格医药 2025三季报 —; 药明康德 2025三季报 46.62%",
       "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, gross_profit_margin FROM core_performance_indicators_sheet WHERE (stock_abbr='凯莱英' OR stock_abbr='药明康德' OR stock_abbr='泰格医药') AND report_year IN (2025) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B3017_1.jpg"
     }
@@ -2462,7 +2591,7 @@
   "子问题": [
     {
       "Q": "药明康德2025年第三季度净利润同比增长情况（与2024年Q3比较）",
-      "A": "净利润同比 对比：药明康德 2024三季报 —; 药明康德 2025三季报 —",
+      "A": "净利润同比 对比：药明康德 2024三季报 —; 药明康德 2025三季报 84.90%",
       "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_profit_yoy_growth FROM income_sheet WHERE (stock_abbr='药明康德') AND report_year IN (2025,2024) AND report_period IN ('Q3') ORDER BY stock_code, report_year, CASE report_period WHEN 'Q1' THEN 1 WHEN 'HY' THEN 2 WHEN 'Q3' THEN 3 WHEN 'FY' THEN 4 END",
       "image": "B3020_1.jpg"
     }
@@ -2492,10 +2621,14 @@
           <t>[{"Q": "2025年第三季度，净利润同比增长率波动最大（绝对值最大）的公司是哪家？展示具体增长率"}]</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr"/>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, stock_code, report_year, report_period, net_profit_yoy_growth, ABS(net_profit_yoy_growth) AS abs_value FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_profit_yoy_growth IS NOT NULL ORDER BY abs_value DESC LIMIT 1</t>
+        </is>
+      </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
@@ -2506,15 +2639,19 @@
   "子问题": [
     {
       "Q": "2025年第三季度，净利润同比增长率波动最大（绝对值最大）的公司是哪家？展示具体增长率",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr"/>
+      "A": "成都先导 2025三季报的净利润同比为 220.10%",
+      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_profit_yoy_growth, ABS(net_profit_yoy_growth) AS abs_value FROM income_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_profit_yoy_growth IS NOT NULL ORDER BY abs_value DESC LIMIT 1",
+      "image": "B3021_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>B3021_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="120" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
@@ -2774,7 +2911,7 @@
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>SELECT stock_abbr, stock_code, report_year, report_period, net_profit_excl_non_recurring FROM core_performance_indicators_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_profit_excl_non_recurring &gt; 5000.0 AND net_profit_excl_non_recurring IS NOT NULL ORDER BY net_profit_excl_non_recurring DESC LIMIT 50</t>
+          <t>SELECT stock_abbr, stock_code, COUNT(*) AS 满足期数 FROM core_performance_indicators_sheet WHERE (report_year BETWEEN 2022 AND 2025 AND net_profit_excl_non_recurring &gt; 5000.0) AND net_profit_excl_non_recurring IS NOT NULL GROUP BY stock_code, stock_abbr HAVING COUNT(*) &gt;= 4 ORDER BY 满足期数 DESC LIMIT 50</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
@@ -2791,7 +2928,7 @@
     {
       "Q": "寻找2022-2025年第三季度连续四个报告期扣非净利润均超过5000万元的公司，列出股票代码和简称",
       "A": "未查询到数据",
-      "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_profit_excl_non_recurring FROM core_performance_indicators_sheet WHERE report_year IN (2025) AND report_period IN ('Q3') AND net_profit_excl_non_recurring &gt; 5000.0 AND net_profit_excl_non_recurring IS NOT NULL ORDER BY net_profit_excl_non_recurring DESC LIMIT 50",
+      "SQL": "SELECT stock_abbr, stock_code, COUNT(*) AS 满足期数 FROM core_performance_indicators_sheet WHERE (report_year BETWEEN 2022 AND 2025 AND net_profit_excl_non_recurring &gt; 5000.0) AND net_profit_excl_non_recurring IS NOT NULL GROUP BY stock_code, stock_abbr HAVING COUNT(*) &gt;= 4 ORDER BY 满足期数 DESC LIMIT 50",
       "image": ""
     }
   ]
@@ -2882,15 +3019,19 @@
   "子问题": [
     {
       "Q": "2025年第三季度，资产-总资产同比增长率超过营业总收入同比增长率的公司有哪些？列出简称",
-      "A": "未查询到数据",
+      "A": "符合条件共 3 家，前3：百克生物(688276) —; 昭衍新药(603127) —; 药明康德(603259) —",
       "SQL": "SELECT t1.stock_abbr, t1.stock_code, t1.report_year, t1.report_period, t1.asset_total_assets_yoy_growth, t2.operating_revenue_yoy_growth FROM balance_sheet t1 JOIN income_sheet t2 USING (stock_code, report_year, report_period) WHERE (t1.report_year IN (2025) AND t1.report_period IN ('Q3')) AND t1.asset_total_assets_yoy_growth IS NOT NULL AND t2.operating_revenue_yoy_growth IS NOT NULL AND t1.asset_total_assets_yoy_growth &gt; t2.operating_revenue_yoy_growth ORDER BY (t1.asset_total_assets_yoy_growth - t2.operating_revenue_yoy_growth) DESC LIMIT 50",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G30" s="1" t="inlineStr"/>
+      "image": "B3029_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>B3029_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="120" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
@@ -3244,10 +3385,14 @@
           <t>[{"Q": "2022-2025年第三季度，营业总收入连续保持正增长的公司有哪些？列出简称"}]</t>
         </is>
       </c>
-      <c r="D38" s="1" t="inlineStr"/>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>SELECT stock_abbr, stock_code, COUNT(*) AS 满足期数 FROM income_sheet WHERE (report_year BETWEEN 2022 AND 2025 AND operating_revenue_yoy_growth &gt; 0) AND operating_revenue_yoy_growth IS NOT NULL GROUP BY stock_code, stock_abbr HAVING COUNT(*) &gt;= 4 ORDER BY 满足期数 DESC LIMIT 50</t>
+        </is>
+      </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
@@ -3258,15 +3403,19 @@
   "子问题": [
     {
       "Q": "2022-2025年第三季度，营业总收入连续保持正增长的公司有哪些？列出简称",
-      "A": "澄清：请问要查询哪家公司？",
-      "SQL": "",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G38" s="1" t="inlineStr"/>
+      "A": "符合条件共 4 家，前4：成都先导(688222) —; 迈普医学(301033) —; 百普赛斯(301080) —; 药明康德(603259) —",
+      "SQL": "SELECT stock_abbr, stock_code, COUNT(*) AS 满足期数 FROM income_sheet WHERE (report_year BETWEEN 2022 AND 2025 AND operating_revenue_yoy_growth &gt; 0) AND operating_revenue_yoy_growth IS NOT NULL GROUP BY stock_code, stock_abbr HAVING COUNT(*) &gt;= 4 ORDER BY 满足期数 DESC LIMIT 50",
+      "image": "B3037_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>B3037_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="120" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
@@ -3730,15 +3879,19 @@
   "子问题": [
     {
       "Q": "比较2024年和2025年第三季度各公司净利润，找出净利润同比增长超过100%的公司",
-      "A": "未查询到数据",
+      "A": "净利润同比 对比：成都先导 2025三季报 220.10%; 昭衍新药 2025三季报 208.70%",
       "SQL": "SELECT stock_abbr, stock_code, report_year, report_period, net_profit_yoy_growth FROM income_sheet WHERE report_year IN (2024,2025) AND report_period IN ('Q3') AND net_profit_yoy_growth &gt; 100.0 AND net_profit_yoy_growth IS NOT NULL ORDER BY net_profit_yoy_growth DESC LIMIT 50",
-      "image": ""
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="G48" s="1" t="inlineStr"/>
+      "image": "B3047_1.jpg"
+    }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>B3047_1.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="120" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
